--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.88624796910404</v>
+        <v>4.044015294979407</v>
       </c>
       <c r="D2" t="n">
-        <v>24.78276839167211</v>
+        <v>4.027199863646719</v>
       </c>
       <c r="E2" t="n">
-        <v>6.33591901592959</v>
+        <v>1.029586840088558</v>
       </c>
       <c r="F2" t="n">
-        <v>6.225342507734133</v>
+        <v>1.011618157506797</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.31237043583374</v>
+        <v>3.950760195822983</v>
       </c>
       <c r="D3" t="n">
-        <v>24.25907645554182</v>
+        <v>3.942099924025546</v>
       </c>
       <c r="E3" t="n">
-        <v>6.33591901592959</v>
+        <v>1.029586840088558</v>
       </c>
       <c r="F3" t="n">
-        <v>6.225342507734133</v>
+        <v>1.011618157506797</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.08676676223066</v>
+        <v>5.539099598862482</v>
       </c>
       <c r="D4" t="n">
-        <v>33.84967920176646</v>
+        <v>5.50057287028705</v>
       </c>
       <c r="E4" t="n">
-        <v>6.33591901592959</v>
+        <v>1.029586840088558</v>
       </c>
       <c r="F4" t="n">
-        <v>6.225342507734133</v>
+        <v>1.011618157506797</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.31957887099583</v>
+        <v>3.301931566536823</v>
       </c>
       <c r="D5" t="n">
-        <v>20.35614999543484</v>
+        <v>3.307874374258162</v>
       </c>
       <c r="E5" t="n">
-        <v>6.33591901592959</v>
+        <v>1.029586840088558</v>
       </c>
       <c r="F5" t="n">
-        <v>6.225342507734133</v>
+        <v>1.011618157506797</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.03952719902041</v>
+        <v>3.581423169840817</v>
       </c>
       <c r="D6" t="n">
-        <v>21.2050332956048</v>
+        <v>3.44581791053578</v>
       </c>
       <c r="E6" t="n">
-        <v>6.33591901592959</v>
+        <v>1.029586840088558</v>
       </c>
       <c r="F6" t="n">
-        <v>6.225342507734133</v>
+        <v>1.011618157506797</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>11.92330419128378</v>
+        <v>1.937536931083615</v>
       </c>
       <c r="D7" t="n">
-        <v>12.49672362938534</v>
+        <v>2.030717589775117</v>
       </c>
       <c r="E7" t="n">
-        <v>6.33591901592959</v>
+        <v>1.029586840088558</v>
       </c>
       <c r="F7" t="n">
-        <v>6.225342507734133</v>
+        <v>1.011618157506797</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.99893805685145</v>
+        <v>4.54982743423836</v>
       </c>
       <c r="D8" t="n">
-        <v>28.58698022431623</v>
+        <v>4.645384286451388</v>
       </c>
       <c r="E8" t="n">
-        <v>6.33591901592959</v>
+        <v>1.029586840088558</v>
       </c>
       <c r="F8" t="n">
-        <v>6.225342507734133</v>
+        <v>1.011618157506797</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
